--- a/main/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/main/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T13:46:42+00:00</t>
+    <t>2026-06-17T14:05:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/main/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T14:05:17+00:00</t>
+    <t>2026-06-17T14:38:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/main/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T14:38:50+00:00</t>
+    <t>2026-06-17T14:43:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/main/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T14:43:38+00:00</t>
+    <t>2026-06-17T15:09:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/main/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T15:09:02+00:00</t>
+    <t>2026-06-19T17:16:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/main/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T17:16:10+00:00</t>
+    <t>2026-06-26T10:38:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/main/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T10:38:02+00:00</t>
+    <t>2026-07-01T08:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/main/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:38:11+00:00</t>
+    <t>2026-07-01T08:43:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/main/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:43:34+00:00</t>
+    <t>2026-07-01T08:44:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/main/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:44:40+00:00</t>
+    <t>2026-07-01T08:45:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/main/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:45:35+00:00</t>
+    <t>2026-07-01T08:46:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/main/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:46:53+00:00</t>
+    <t>2026-07-01T08:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/main/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:57:39+00:00</t>
+    <t>2026-07-01T10:07:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/main/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T10:07:08+00:00</t>
+    <t>2026-07-01T10:07:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/main/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T10:07:52+00:00</t>
+    <t>2026-07-01T10:09:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/main/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T10:09:02+00:00</t>
+    <t>2026-07-01T12:36:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/main/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T12:36:12+00:00</t>
+    <t>2026-07-01T13:39:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/main/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:39:29+00:00</t>
+    <t>2026-07-02T11:54:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-DocumentEntry.xlsx
+++ b/main/ig/StructureDefinition-DocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-02T11:54:51+00:00</t>
+    <t>2026-07-16T07:22:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -506,7 +506,7 @@
     <t>**Format Code**</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J10-XdsFormatCode-CISIS/FHIR/JDV-J10-XdsFormatCode-CISIS|20251029120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J10-XdsFormatCode-CISIS/FHIR/JDV-J10-XdsFormatCode-CISIS|20260629120000</t>
   </si>
   <si>
     <t>DocumentEntry.healthcareFacilityTypeCode</t>
@@ -542,7 +542,7 @@
     <t>**Type Code**</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J07-XdsTypeCode-CISIS/FHIR/JDV-J07-XdsTypeCode-CISIS|20260601120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J07-XdsTypeCode-CISIS/FHIR/JDV-J07-XdsTypeCode-CISIS|20260629120000</t>
   </si>
   <si>
     <t>DocumentEntry.documentAvailability</t>
